--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Water quality\Data\Raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BD0687F-DD89-4C95-A9CB-3D9447E6645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7990421-3CCE-471C-A4D7-EB3E7591E5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
   <si>
     <t>Site</t>
   </si>
@@ -89,19 +89,58 @@
   </si>
   <si>
     <t>S97_S</t>
+  </si>
+  <si>
+    <t>WI</t>
+  </si>
+  <si>
+    <t>USGS-02313272</t>
+  </si>
+  <si>
+    <t>USGS-285447082445100</t>
+  </si>
+  <si>
+    <t>USGS-285531082412600</t>
+  </si>
+  <si>
+    <t>USGS-02310712</t>
+  </si>
+  <si>
+    <t>USGS-284506082435801</t>
+  </si>
+  <si>
+    <t>USGS-02310752</t>
+  </si>
+  <si>
+    <t>USGS-02313250</t>
+  </si>
+  <si>
+    <t>USGS-02310750</t>
+  </si>
+  <si>
+    <t>USGS-02313230</t>
+  </si>
+  <si>
+    <t>USGS-02310700</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF1B1B1B"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -124,8 +163,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -422,13 +462,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E15"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +485,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -462,7 +502,7 @@
         <v>-83.377499999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -479,7 +519,7 @@
         <v>-83.086667000000006</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -496,7 +536,7 @@
         <v>-82.769001071597003</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -513,7 +553,7 @@
         <v>-83.162099999999995</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -530,7 +570,7 @@
         <v>-83.062749999999994</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -547,7 +587,7 @@
         <v>-83.241699999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -564,7 +604,7 @@
         <v>-83.341700000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -581,7 +621,7 @@
         <v>-83.022779999999997</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -598,7 +638,7 @@
         <v>-80.288118999999995</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -615,7 +655,7 @@
         <v>-80.258364</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -632,7 +672,7 @@
         <v>-80.207002000000003</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -649,7 +689,7 @@
         <v>-80.359804999999994</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -666,7 +706,7 @@
         <v>-80.285263</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -681,6 +721,244 @@
       </c>
       <c r="E15">
         <v>-80.34066</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>23</v>
+      </c>
+      <c r="B16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1">
+        <v>29.204133775691599</v>
+      </c>
+      <c r="E16" s="1">
+        <v>-82.769001071597003</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>23</v>
+      </c>
+      <c r="B17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="1">
+        <v>29.204133775691599</v>
+      </c>
+      <c r="E17" s="1">
+        <v>-82.769001071597003</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>23</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1">
+        <v>29.001128728537498</v>
+      </c>
+      <c r="E18">
+        <v>-82.765833008482403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19" t="s">
+        <v>25</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="1">
+        <v>28.911691666666599</v>
+      </c>
+      <c r="E19">
+        <v>-82.747638888888801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20" s="1">
+        <v>28.925277777777801</v>
+      </c>
+      <c r="E20">
+        <v>-82.690638888888898</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" s="1">
+        <v>28.7716664406531</v>
+      </c>
+      <c r="E21">
+        <v>-82.695706281747107</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>28</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="1">
+        <v>28.751583333333301</v>
+      </c>
+      <c r="E22">
+        <v>-82.732891666666603</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" s="1">
+        <v>28.9015555555555</v>
+      </c>
+      <c r="E23">
+        <v>-82.645805555555498</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>30</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" s="1">
+        <v>29.0210853789327</v>
+      </c>
+      <c r="E24">
+        <v>-82.637881756271497</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" s="1">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="E25">
+        <v>-82.635188270857199</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="1">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="E26">
+        <v>-82.635188270857199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="1">
+        <v>29.0099748538913</v>
+      </c>
+      <c r="E27">
+        <v>-82.616769865935098</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>23</v>
+      </c>
+      <c r="B28" t="s">
+        <v>33</v>
+      </c>
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" s="1">
+        <v>28.785277047241902</v>
+      </c>
+      <c r="E28">
+        <v>-82.617926267019001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" t="s">
+        <v>33</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29" s="1">
+        <v>28.785277047241902</v>
+      </c>
+      <c r="E29">
+        <v>-82.617926267019001</v>
       </c>
     </row>
   </sheetData>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Water quality\Data\Raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7990421-3CCE-471C-A4D7-EB3E7591E5BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F316F-DBBC-4310-8F25-C6997DC2347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="35">
   <si>
     <t>Site</t>
   </si>
@@ -122,6 +122,9 @@
   </si>
   <si>
     <t>USGS-02310700</t>
+  </si>
+  <si>
+    <t>HO</t>
   </si>
 </sst>
 </file>
@@ -810,7 +813,7 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -929,7 +932,7 @@
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B28" t="s">
         <v>33</v>
@@ -946,7 +949,7 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="B29" t="s">
         <v>33</v>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -1,26 +1,39 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Water quality\Data\Raw-data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F316F-DBBC-4310-8F25-C6997DC2347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{193E05E8-4DDE-4A73-87FF-6E2AEAA502F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="46">
   <si>
     <t>Site</t>
   </si>
@@ -125,13 +138,46 @@
   </si>
   <si>
     <t>HO</t>
+  </si>
+  <si>
+    <t>S49_R</t>
+  </si>
+  <si>
+    <t>Rain</t>
+  </si>
+  <si>
+    <t>S97_R</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>US1</t>
+  </si>
+  <si>
+    <t>A1A</t>
+  </si>
+  <si>
+    <t>S49</t>
+  </si>
+  <si>
+    <t>S80</t>
+  </si>
+  <si>
+    <t>S97</t>
+  </si>
+  <si>
+    <t>USGS-02277110</t>
+  </si>
+  <si>
+    <t>USGS-02277100</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -143,6 +189,12 @@
       <sz val="10"/>
       <color rgb="FF1B1B1B"/>
       <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF334155"/>
+      <name val="Verdana"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -166,9 +218,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -465,13 +518,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:F33"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -487,8 +540,11 @@
       <c r="E1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -504,8 +560,11 @@
       <c r="E2">
         <v>-83.377499999999998</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -521,8 +580,11 @@
       <c r="E3">
         <v>-83.086667000000006</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -538,8 +600,11 @@
       <c r="E4">
         <v>-82.769001071597003</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -555,8 +620,11 @@
       <c r="E5">
         <v>-83.162099999999995</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -572,8 +640,11 @@
       <c r="E6">
         <v>-83.062749999999994</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -589,8 +660,11 @@
       <c r="E7">
         <v>-83.241699999999994</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -606,8 +680,11 @@
       <c r="E8">
         <v>-83.341700000000003</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -623,8 +700,11 @@
       <c r="E9">
         <v>-83.022779999999997</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -640,8 +720,11 @@
       <c r="E10">
         <v>-80.288118999999995</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -657,8 +740,11 @@
       <c r="E11">
         <v>-80.258364</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -674,8 +760,11 @@
       <c r="E12">
         <v>-80.207002000000003</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -691,8 +780,11 @@
       <c r="E13">
         <v>-80.359804999999994</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -708,8 +800,11 @@
       <c r="E14">
         <v>-80.285263</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -725,8 +820,11 @@
       <c r="E15">
         <v>-80.34066</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -742,8 +840,11 @@
       <c r="E16" s="1">
         <v>-82.769001071597003</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -759,8 +860,11 @@
       <c r="E17" s="1">
         <v>-82.769001071597003</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -776,8 +880,11 @@
       <c r="E18">
         <v>-82.765833008482403</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -793,8 +900,11 @@
       <c r="E19">
         <v>-82.747638888888801</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -810,8 +920,11 @@
       <c r="E20">
         <v>-82.690638888888898</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -827,8 +940,11 @@
       <c r="E21">
         <v>-82.695706281747107</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -844,8 +960,11 @@
       <c r="E22">
         <v>-82.732891666666603</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
@@ -861,8 +980,11 @@
       <c r="E23">
         <v>-82.645805555555498</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>23</v>
       </c>
@@ -878,8 +1000,11 @@
       <c r="E24">
         <v>-82.637881756271497</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
@@ -895,8 +1020,11 @@
       <c r="E25">
         <v>-82.635188270857199</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>23</v>
       </c>
@@ -912,8 +1040,11 @@
       <c r="E26">
         <v>-82.635188270857199</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>23</v>
       </c>
@@ -929,8 +1060,11 @@
       <c r="E27">
         <v>-82.616769865935098</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>34</v>
       </c>
@@ -946,8 +1080,11 @@
       <c r="E28">
         <v>-82.617926267019001</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>34</v>
       </c>
@@ -962,6 +1099,89 @@
       </c>
       <c r="E29">
         <v>-82.617926267019001</v>
+      </c>
+      <c r="F29" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>36</v>
+      </c>
+      <c r="D30" s="2">
+        <v>27.261139</v>
+      </c>
+      <c r="E30" s="2">
+        <v>-80.359397000000001</v>
+      </c>
+      <c r="F30" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>36</v>
+      </c>
+      <c r="D31">
+        <v>27.205774999999999</v>
+      </c>
+      <c r="E31">
+        <v>-80.340772000000001</v>
+      </c>
+      <c r="F31" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>27.199384999999999</v>
+      </c>
+      <c r="E32">
+        <v>-80.207002000000003</v>
+      </c>
+      <c r="F32" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33">
+        <v>27.201958000000001</v>
+      </c>
+      <c r="E33">
+        <v>-80.258364</v>
+      </c>
+      <c r="F33" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -1,149 +1,136 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Water quality\Data\Raw-data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F316F-DBBC-4310-8F25-C6997DC2347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="35">
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>StationID</t>
-  </si>
-  <si>
-    <t>DataType</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>USGS-02324170</t>
-  </si>
-  <si>
-    <t>Flow</t>
-  </si>
-  <si>
-    <t>USGS-02323592</t>
-  </si>
-  <si>
-    <t>USGS-02313700</t>
-  </si>
-  <si>
-    <t>SSSal1</t>
-  </si>
-  <si>
-    <t>Salinity</t>
-  </si>
-  <si>
-    <t>SSSal2</t>
-  </si>
-  <si>
-    <t>SSSal3</t>
-  </si>
-  <si>
-    <t>SSSal4</t>
-  </si>
-  <si>
-    <t>SSSal5</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>HR1</t>
-  </si>
-  <si>
-    <t>STL_RIVER</t>
-  </si>
-  <si>
-    <t>STL-STPT</t>
-  </si>
-  <si>
-    <t>S49_S</t>
-  </si>
-  <si>
-    <t>S80_S</t>
-  </si>
-  <si>
-    <t>S97_S</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>USGS-02313272</t>
-  </si>
-  <si>
-    <t>USGS-285447082445100</t>
-  </si>
-  <si>
-    <t>USGS-285531082412600</t>
-  </si>
-  <si>
-    <t>USGS-02310712</t>
-  </si>
-  <si>
-    <t>USGS-284506082435801</t>
-  </si>
-  <si>
-    <t>USGS-02310752</t>
-  </si>
-  <si>
-    <t>USGS-02313250</t>
-  </si>
-  <si>
-    <t>USGS-02310750</t>
-  </si>
-  <si>
-    <t>USGS-02313230</t>
-  </si>
-  <si>
-    <t>USGS-02310700</t>
-  </si>
-  <si>
-    <t>HO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StationID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02324170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02323592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STL_RIVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STL-STPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S49_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S80_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S97_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-285447082445100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-285531082412600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-284506082435801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310700</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1B1B1B"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,23 +153,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -464,14 +441,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +462,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -498,14 +472,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>29.668056</v>
       </c>
-      <c r="E2">
-        <v>-83.377499999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" t="n">
+        <v>-83.3775</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -515,14 +489,14 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>29.339167</v>
       </c>
-      <c r="E3">
-        <v>-83.086667000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E3" t="n">
+        <v>-83.086667</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -532,14 +506,14 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E4">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -549,14 +523,14 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>29.299849999999999</v>
-      </c>
-      <c r="E5">
-        <v>-83.162099999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" t="n">
+        <v>29.29985</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.1621</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -566,14 +540,14 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>29.15558</v>
       </c>
-      <c r="E6">
-        <v>-83.062749999999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" t="n">
+        <v>-83.06275</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -583,14 +557,14 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>29.3917</v>
       </c>
-      <c r="E7">
-        <v>-83.241699999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" t="n">
+        <v>-83.2417</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -600,14 +574,14 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8">
-        <v>29.441700000000001</v>
-      </c>
-      <c r="E8">
-        <v>-83.341700000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" t="n">
+        <v>29.4417</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.3417</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -617,14 +591,14 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9">
-        <v>29.399170000000002</v>
-      </c>
-      <c r="E9">
-        <v>-83.022779999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" t="n">
+        <v>29.39917</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.02278</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -634,14 +608,14 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>27.22814</v>
       </c>
-      <c r="E10">
-        <v>-80.288118999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="n">
+        <v>-80.288119</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -651,14 +625,14 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11">
-        <v>27.201958000000001</v>
-      </c>
-      <c r="E11">
+      <c r="D11" t="n">
+        <v>27.201958</v>
+      </c>
+      <c r="E11" t="n">
         <v>-80.258364</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -668,14 +642,14 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>27.199384999999999</v>
-      </c>
-      <c r="E12">
-        <v>-80.207002000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" t="n">
+        <v>27.199385</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-80.207002</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -685,14 +659,14 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13">
-        <v>27.261393000000002</v>
-      </c>
-      <c r="E13">
-        <v>-80.359804999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" t="n">
+        <v>27.261393</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-80.359805</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -702,14 +676,14 @@
       <c r="C14" t="s">
         <v>7</v>
       </c>
-      <c r="D14">
-        <v>27.111789000000002</v>
-      </c>
-      <c r="E14">
+      <c r="D14" t="n">
+        <v>27.111789</v>
+      </c>
+      <c r="E14" t="n">
         <v>-80.285263</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -719,14 +693,14 @@
       <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="D15">
-        <v>27.205549000000001</v>
-      </c>
-      <c r="E15">
+      <c r="D15" t="n">
+        <v>27.205549</v>
+      </c>
+      <c r="E15" t="n">
         <v>-80.34066</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -736,14 +710,14 @@
       <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="1">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E16" s="1">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D16" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -753,14 +727,14 @@
       <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="1">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E17" s="1">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -770,14 +744,14 @@
       <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="1">
-        <v>29.001128728537498</v>
-      </c>
-      <c r="E18">
-        <v>-82.765833008482403</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D18" t="n">
+        <v>29.0011287285375</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.7658330084824</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -787,14 +761,14 @@
       <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="1">
-        <v>28.911691666666599</v>
-      </c>
-      <c r="E19">
-        <v>-82.747638888888801</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" t="n">
+        <v>28.9116916666666</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.7476388888888</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -804,168 +778,168 @@
       <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="1">
-        <v>28.925277777777801</v>
-      </c>
-      <c r="E20">
-        <v>-82.690638888888898</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D20" t="n">
+        <v>28.9252777777778</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.6906388888889</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21" t="n">
+        <v>28.7716664406531</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-82.6957062817471</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>23</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" t="n">
+        <v>28.7515833333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-82.7328916666666</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23" t="n">
+        <v>28.9015555555555</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-82.6458055555555</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>31</v>
+      </c>
+      <c r="C24" t="s">
+        <v>7</v>
+      </c>
+      <c r="D24" t="n">
+        <v>29.0210853789327</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-82.6378817562715</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B25" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25" t="n">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-82.6351882708572</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="n">
+        <v>28.9050034928561</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-82.6351882708572</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>33</v>
+      </c>
+      <c r="C27" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" t="n">
+        <v>29.0099748538913</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-82.6167698659351</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>34</v>
       </c>
-      <c r="B21" t="s">
+      <c r="C28" t="s">
+        <v>7</v>
+      </c>
+      <c r="D28" t="n">
+        <v>28.7852770472419</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-82.617926267019</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
         <v>27</v>
       </c>
-      <c r="C21" t="s">
-        <v>11</v>
-      </c>
-      <c r="D21" s="1">
-        <v>28.7716664406531</v>
-      </c>
-      <c r="E21">
-        <v>-82.695706281747107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>23</v>
-      </c>
-      <c r="B22" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="1">
-        <v>28.751583333333301</v>
-      </c>
-      <c r="E22">
-        <v>-82.732891666666603</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>29</v>
-      </c>
-      <c r="C23" t="s">
-        <v>11</v>
-      </c>
-      <c r="D23" s="1">
-        <v>28.9015555555555</v>
-      </c>
-      <c r="E23">
-        <v>-82.645805555555498</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>30</v>
-      </c>
-      <c r="C24" t="s">
-        <v>7</v>
-      </c>
-      <c r="D24" s="1">
-        <v>29.0210853789327</v>
-      </c>
-      <c r="E24">
-        <v>-82.637881756271497</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" t="s">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="1">
-        <v>28.9050034928561</v>
-      </c>
-      <c r="E25">
-        <v>-82.635188270857199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" t="s">
-        <v>31</v>
-      </c>
-      <c r="C26" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="1">
-        <v>28.9050034928561</v>
-      </c>
-      <c r="E26">
-        <v>-82.635188270857199</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
-        <v>23</v>
-      </c>
-      <c r="B27" t="s">
-        <v>32</v>
-      </c>
-      <c r="C27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D27" s="1">
-        <v>29.0099748538913</v>
-      </c>
-      <c r="E27">
-        <v>-82.616769865935098</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+      <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="B28" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" t="s">
-        <v>7</v>
-      </c>
-      <c r="D28" s="1">
-        <v>28.785277047241902</v>
-      </c>
-      <c r="E28">
-        <v>-82.617926267019001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="1">
-        <v>28.785277047241902</v>
-      </c>
-      <c r="E29">
-        <v>-82.617926267019001</v>
+      <c r="D29" t="n">
+        <v>28.7852770472419</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-82.617926267019</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -117,6 +117,24 @@
   </si>
   <si>
     <t xml:space="preserve">USGS-02310700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WISal6</t>
   </si>
 </sst>
 </file>
@@ -938,6 +956,108 @@
         <v>-82.617926267019</v>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" t="s">
+        <v>35</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30" t="n">
+        <v>28.90296</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-82.64148</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" t="s">
+        <v>36</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31" t="n">
+        <v>29.00113</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-82.76583</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B32" t="s">
+        <v>37</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32" t="n">
+        <v>29.20413</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-82.769</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>23</v>
+      </c>
+      <c r="B33" t="s">
+        <v>38</v>
+      </c>
+      <c r="C33" t="s">
+        <v>11</v>
+      </c>
+      <c r="D33" t="n">
+        <v>28.92528</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-82.69064</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>23</v>
+      </c>
+      <c r="B34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="n">
+        <v>28.91169</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-82.74764</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>23</v>
+      </c>
+      <c r="B35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C35" t="s">
+        <v>11</v>
+      </c>
+      <c r="D35" t="n">
+        <v>28.75158</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-82.73289</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -1,149 +1,250 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
-  <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\HSM-and-mapping\Water quality\Data\Raw-data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E7F316F-DBBC-4310-8F25-C6997DC2347F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookPr date1904="false"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet 1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="35">
-  <si>
-    <t>Site</t>
-  </si>
-  <si>
-    <t>StationID</t>
-  </si>
-  <si>
-    <t>DataType</t>
-  </si>
-  <si>
-    <t>Latitude</t>
-  </si>
-  <si>
-    <t>Longitude</t>
-  </si>
-  <si>
-    <t>SS</t>
-  </si>
-  <si>
-    <t>USGS-02324170</t>
-  </si>
-  <si>
-    <t>Flow</t>
-  </si>
-  <si>
-    <t>USGS-02323592</t>
-  </si>
-  <si>
-    <t>USGS-02313700</t>
-  </si>
-  <si>
-    <t>SSSal1</t>
-  </si>
-  <si>
-    <t>Salinity</t>
-  </si>
-  <si>
-    <t>SSSal2</t>
-  </si>
-  <si>
-    <t>SSSal3</t>
-  </si>
-  <si>
-    <t>SSSal4</t>
-  </si>
-  <si>
-    <t>SSSal5</t>
-  </si>
-  <si>
-    <t>SL</t>
-  </si>
-  <si>
-    <t>HR1</t>
-  </si>
-  <si>
-    <t>STL_RIVER</t>
-  </si>
-  <si>
-    <t>STL-STPT</t>
-  </si>
-  <si>
-    <t>S49_S</t>
-  </si>
-  <si>
-    <t>S80_S</t>
-  </si>
-  <si>
-    <t>S97_S</t>
-  </si>
-  <si>
-    <t>WI</t>
-  </si>
-  <si>
-    <t>USGS-02313272</t>
-  </si>
-  <si>
-    <t>USGS-285447082445100</t>
-  </si>
-  <si>
-    <t>USGS-285531082412600</t>
-  </si>
-  <si>
-    <t>USGS-02310712</t>
-  </si>
-  <si>
-    <t>USGS-284506082435801</t>
-  </si>
-  <si>
-    <t>USGS-02310752</t>
-  </si>
-  <si>
-    <t>USGS-02313250</t>
-  </si>
-  <si>
-    <t>USGS-02310750</t>
-  </si>
-  <si>
-    <t>USGS-02313230</t>
-  </si>
-  <si>
-    <t>USGS-02310700</t>
-  </si>
-  <si>
-    <t>HO</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+  <si>
+    <t xml:space="preserve">Site</t>
+  </si>
+  <si>
+    <t xml:space="preserve">StationID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DataType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longitude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02324170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02323592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salinity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSSal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HR1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STL_RIVER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STL-STPT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S49_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S80_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S97_S</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-285447082445100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-285531082412600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-284506082435801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313250</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02313230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02310700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02369600</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02370140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02370500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02376033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02376115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02377750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PESal9</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1B1B1B"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -166,23 +267,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -464,14 +555,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E29"/>
-  <sheetFormatPr defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -488,7 +576,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -498,14 +586,14 @@
       <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2">
+      <c r="D2" t="n">
         <v>29.668056</v>
       </c>
-      <c r="E2">
-        <v>-83.377499999999998</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E2" t="n">
+        <v>-83.3775</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -515,14 +603,14 @@
       <c r="C3" t="s">
         <v>7</v>
       </c>
-      <c r="D3">
+      <c r="D3" t="n">
         <v>29.339167</v>
       </c>
-      <c r="E3">
-        <v>-83.086667000000006</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E3" t="n">
+        <v>-83.086667</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -532,14 +620,14 @@
       <c r="C4" t="s">
         <v>7</v>
       </c>
-      <c r="D4">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E4">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D4" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -549,14 +637,14 @@
       <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="D5">
-        <v>29.299849999999999</v>
-      </c>
-      <c r="E5">
-        <v>-83.162099999999995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D5" t="n">
+        <v>29.29985</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-83.1621</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -566,14 +654,14 @@
       <c r="C6" t="s">
         <v>11</v>
       </c>
-      <c r="D6">
+      <c r="D6" t="n">
         <v>29.15558</v>
       </c>
-      <c r="E6">
-        <v>-83.062749999999994</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E6" t="n">
+        <v>-83.06275</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -583,14 +671,14 @@
       <c r="C7" t="s">
         <v>11</v>
       </c>
-      <c r="D7">
+      <c r="D7" t="n">
         <v>29.3917</v>
       </c>
-      <c r="E7">
-        <v>-83.241699999999994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E7" t="n">
+        <v>-83.2417</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -600,14 +688,14 @@
       <c r="C8" t="s">
         <v>11</v>
       </c>
-      <c r="D8">
-        <v>29.441700000000001</v>
-      </c>
-      <c r="E8">
-        <v>-83.341700000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D8" t="n">
+        <v>29.4417</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-83.3417</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
         <v>5</v>
       </c>
@@ -617,14 +705,14 @@
       <c r="C9" t="s">
         <v>11</v>
       </c>
-      <c r="D9">
-        <v>29.399170000000002</v>
-      </c>
-      <c r="E9">
-        <v>-83.022779999999997</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D9" t="n">
+        <v>29.39917</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-83.02278</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
         <v>16</v>
       </c>
@@ -634,14 +722,14 @@
       <c r="C10" t="s">
         <v>11</v>
       </c>
-      <c r="D10">
+      <c r="D10" t="n">
         <v>27.22814</v>
       </c>
-      <c r="E10">
-        <v>-80.288118999999995</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E10" t="n">
+        <v>-80.288119</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
         <v>16</v>
       </c>
@@ -651,14 +739,14 @@
       <c r="C11" t="s">
         <v>11</v>
       </c>
-      <c r="D11">
-        <v>27.201958000000001</v>
-      </c>
-      <c r="E11">
+      <c r="D11" t="n">
+        <v>27.201958</v>
+      </c>
+      <c r="E11" t="n">
         <v>-80.258364</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -668,14 +756,14 @@
       <c r="C12" t="s">
         <v>11</v>
       </c>
-      <c r="D12">
-        <v>27.199384999999999</v>
-      </c>
-      <c r="E12">
-        <v>-80.207002000000003</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D12" t="n">
+        <v>27.199385</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-80.207002</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -685,14 +773,14 @@
       <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13">
-        <v>27.261393000000002</v>
-      </c>
-      <c r="E13">
-        <v>-80.359804999999994</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D13" t="n">
+        <v>27.261393</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-80.359805</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -702,14 +790,14 @@
       <c r="C14" t="s">
         <v>7</v>
       </c>
-      <c r="D14">
-        <v>27.111789000000002</v>
-      </c>
-      <c r="E14">
+      <c r="D14" t="n">
+        <v>27.111789</v>
+      </c>
+      <c r="E14" t="n">
         <v>-80.285263</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -719,14 +807,14 @@
       <c r="C15" t="s">
         <v>7</v>
       </c>
-      <c r="D15">
-        <v>27.205549000000001</v>
-      </c>
-      <c r="E15">
+      <c r="D15" t="n">
+        <v>27.205549</v>
+      </c>
+      <c r="E15" t="n">
         <v>-80.34066</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -736,14 +824,14 @@
       <c r="C16" t="s">
         <v>7</v>
       </c>
-      <c r="D16" s="1">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E16" s="1">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D16" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -753,14 +841,14 @@
       <c r="C17" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="1">
-        <v>29.204133775691599</v>
-      </c>
-      <c r="E17" s="1">
-        <v>-82.769001071597003</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D17" t="n">
+        <v>29.2041337756916</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-82.769001071597</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
         <v>23</v>
       </c>
@@ -770,14 +858,14 @@
       <c r="C18" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="1">
-        <v>29.001128728537498</v>
-      </c>
-      <c r="E18">
-        <v>-82.765833008482403</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D18" t="n">
+        <v>29.0011287285375</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-82.7658330084824</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
         <v>23</v>
       </c>
@@ -787,14 +875,14 @@
       <c r="C19" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="1">
-        <v>28.911691666666599</v>
-      </c>
-      <c r="E19">
-        <v>-82.747638888888801</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D19" t="n">
+        <v>28.9116916666666</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-82.7476388888888</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -804,168 +892,797 @@
       <c r="C20" t="s">
         <v>11</v>
       </c>
-      <c r="D20" s="1">
-        <v>28.925277777777801</v>
-      </c>
-      <c r="E20">
-        <v>-82.690638888888898</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D20" t="n">
+        <v>28.9252777777778</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.6906388888889</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
         <v>11</v>
       </c>
-      <c r="D21" s="1">
+      <c r="D21" t="n">
         <v>28.7716664406531</v>
       </c>
-      <c r="E21">
-        <v>-82.695706281747107</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E21" t="n">
+        <v>-82.6957062817471</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
         <v>23</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C22" t="s">
         <v>11</v>
       </c>
-      <c r="D22" s="1">
-        <v>28.751583333333301</v>
-      </c>
-      <c r="E22">
-        <v>-82.732891666666603</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D22" t="n">
+        <v>28.7515833333333</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-82.7328916666666</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C23" t="s">
         <v>11</v>
       </c>
-      <c r="D23" s="1">
+      <c r="D23" t="n">
         <v>28.9015555555555</v>
       </c>
-      <c r="E23">
-        <v>-82.645805555555498</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E23" t="n">
+        <v>-82.6458055555555</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>7</v>
       </c>
-      <c r="D24" s="1">
+      <c r="D24" t="n">
         <v>29.0210853789327</v>
       </c>
-      <c r="E24">
-        <v>-82.637881756271497</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E24" t="n">
+        <v>-82.6378817562715</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C25" t="s">
         <v>11</v>
       </c>
-      <c r="D25" s="1">
+      <c r="D25" t="n">
         <v>28.9050034928561</v>
       </c>
-      <c r="E25">
-        <v>-82.635188270857199</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E25" t="n">
+        <v>-82.6351882708572</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
         <v>23</v>
       </c>
       <c r="B26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" t="s">
         <v>7</v>
       </c>
-      <c r="D26" s="1">
+      <c r="D26" t="n">
         <v>28.9050034928561</v>
       </c>
-      <c r="E26">
-        <v>-82.635188270857199</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E26" t="n">
+        <v>-82.6351882708572</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
         <v>23</v>
       </c>
       <c r="B27" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C27" t="s">
         <v>7</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D27" t="n">
         <v>29.0099748538913</v>
       </c>
-      <c r="E27">
-        <v>-82.616769865935098</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E27" t="n">
+        <v>-82.6167698659351</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
         <v>34</v>
-      </c>
-      <c r="B28" t="s">
-        <v>33</v>
       </c>
       <c r="C28" t="s">
         <v>7</v>
       </c>
-      <c r="D28" s="1">
-        <v>28.785277047241902</v>
-      </c>
-      <c r="E28">
-        <v>-82.617926267019001</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="D28" t="n">
+        <v>28.7852770472419</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-82.617926267019</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
+        <v>27</v>
+      </c>
+      <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="B29" t="s">
-        <v>33</v>
-      </c>
       <c r="C29" t="s">
         <v>11</v>
       </c>
-      <c r="D29" s="1">
-        <v>28.785277047241902</v>
-      </c>
-      <c r="E29">
-        <v>-82.617926267019001</v>
+      <c r="D29" t="n">
+        <v>28.7852770472419</v>
+      </c>
+      <c r="E29" t="n">
+        <v>-82.617926267019</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>35</v>
+      </c>
+      <c r="B30" t="s">
+        <v>36</v>
+      </c>
+      <c r="C30" t="s">
+        <v>7</v>
+      </c>
+      <c r="D30" t="n">
+        <v>30.5696390104681</v>
+      </c>
+      <c r="E30" t="n">
+        <v>-86.9235732496926</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>7</v>
+      </c>
+      <c r="D31" t="n">
+        <v>30.704722</v>
+      </c>
+      <c r="E31" t="n">
+        <v>-86.881722</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>38</v>
+      </c>
+      <c r="C32" t="s">
+        <v>7</v>
+      </c>
+      <c r="D32" t="n">
+        <v>30.7085237472786</v>
+      </c>
+      <c r="E32" t="n">
+        <v>-86.9721860089716</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" t="s">
+        <v>39</v>
+      </c>
+      <c r="C33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D33" t="n">
+        <v>30.6701917020841</v>
+      </c>
+      <c r="E33" t="n">
+        <v>-87.2669178727149</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" t="s">
+        <v>40</v>
+      </c>
+      <c r="C34" t="s">
+        <v>7</v>
+      </c>
+      <c r="D34" t="n">
+        <v>30.4982515885812</v>
+      </c>
+      <c r="E34" t="n">
+        <v>-87.3358086143744</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C35" t="s">
+        <v>7</v>
+      </c>
+      <c r="D35" t="n">
+        <v>30.5182508885234</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-87.4627577475218</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30.33436</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-87.15201</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>11</v>
+      </c>
+      <c r="D37" t="n">
+        <v>30.37569</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-87.08581</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" t="n">
+        <v>30.59383</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-87.17464</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>35</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>11</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30.39928</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-86.88566</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>35</v>
+      </c>
+      <c r="B40" t="s">
+        <v>46</v>
+      </c>
+      <c r="C40" t="s">
+        <v>11</v>
+      </c>
+      <c r="D40" t="n">
+        <v>30.46683</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-87.122</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>35</v>
+      </c>
+      <c r="B41" t="s">
+        <v>47</v>
+      </c>
+      <c r="C41" t="s">
+        <v>11</v>
+      </c>
+      <c r="D41" t="n">
+        <v>30.4005</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-87.159</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" t="s">
+        <v>48</v>
+      </c>
+      <c r="C42" t="s">
+        <v>11</v>
+      </c>
+      <c r="D42" t="n">
+        <v>30.4275</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-87.05433</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>11</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30.38628</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-86.99036</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>50</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30.38624</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-86.94531</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="n">
+        <v>30.45328</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-87.33808</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>30.41945</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-86.61981</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="n">
+        <v>30.39475</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-87.27621</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30.56477</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-87.24811</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="s">
+        <v>55</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="n">
+        <v>30.50267</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-87.33458</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>35</v>
+      </c>
+      <c r="B50" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="n">
+        <v>30.54898</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-87.32037</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>35</v>
+      </c>
+      <c r="B51" t="s">
+        <v>57</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="n">
+        <v>30.3673</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-87.3492</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>35</v>
+      </c>
+      <c r="B52" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>30.35185</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-87.41209</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>35</v>
+      </c>
+      <c r="B53" t="s">
+        <v>59</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>30.57215</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-87.40316</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>35</v>
+      </c>
+      <c r="B54" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="n">
+        <v>30.43398</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-86.93604</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>35</v>
+      </c>
+      <c r="B55" t="s">
+        <v>61</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>30.60674</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-87.05934</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>30.57895</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-86.90017</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>35</v>
+      </c>
+      <c r="B57" t="s">
+        <v>63</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="n">
+        <v>30.57784</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-86.93063</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>35</v>
+      </c>
+      <c r="B58" t="s">
+        <v>64</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30.52219</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-87.15134</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>35</v>
+      </c>
+      <c r="B59" t="s">
+        <v>65</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30.61932</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-86.85376</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>35</v>
+      </c>
+      <c r="B60" t="s">
+        <v>66</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="n">
+        <v>30.4023</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-87.4265</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>35</v>
+      </c>
+      <c r="B61" t="s">
+        <v>67</v>
+      </c>
+      <c r="C61" t="s">
+        <v>11</v>
+      </c>
+      <c r="D61" t="n">
+        <v>30.45499</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-87.20792</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>35</v>
+      </c>
+      <c r="B62" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" t="s">
+        <v>11</v>
+      </c>
+      <c r="D62" t="n">
+        <v>30.55064</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-87.22112</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>35</v>
+      </c>
+      <c r="B63" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" t="s">
+        <v>11</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30.44008</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-86.86651</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>35</v>
+      </c>
+      <c r="B64" t="s">
+        <v>70</v>
+      </c>
+      <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="n">
+        <v>30.62231</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-87.03528</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>35</v>
+      </c>
+      <c r="B65" t="s">
+        <v>71</v>
+      </c>
+      <c r="C65" t="s">
+        <v>11</v>
+      </c>
+      <c r="D65" t="n">
+        <v>30.45152</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-86.90558</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>35</v>
+      </c>
+      <c r="B66" t="s">
+        <v>72</v>
+      </c>
+      <c r="C66" t="s">
+        <v>11</v>
+      </c>
+      <c r="D66" t="n">
+        <v>30.53712</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-87.02988</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -135,6 +135,24 @@
   </si>
   <si>
     <t xml:space="preserve">WISal6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02359500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-295308085143700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-295323085151700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-301116085443000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SA</t>
   </si>
 </sst>
 </file>
@@ -1058,6 +1076,142 @@
         <v>-82.73289</v>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" t="s">
+        <v>42</v>
+      </c>
+      <c r="C36" t="s">
+        <v>7</v>
+      </c>
+      <c r="D36" t="n">
+        <v>30.384640616919</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-85.5565932283707</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37" t="s">
+        <v>43</v>
+      </c>
+      <c r="C37" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37" t="n">
+        <v>29.8855555555556</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-85.2436111111111</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>44</v>
+      </c>
+      <c r="C38" t="s">
+        <v>7</v>
+      </c>
+      <c r="D38" t="n">
+        <v>29.8897222222222</v>
+      </c>
+      <c r="E38" t="n">
+        <v>-85.2547222222222</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>41</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>7</v>
+      </c>
+      <c r="D39" t="n">
+        <v>30.1878333333333</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-85.7416666666667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>46</v>
+      </c>
+      <c r="B40" t="s">
+        <v>42</v>
+      </c>
+      <c r="C40" t="s">
+        <v>7</v>
+      </c>
+      <c r="D40" t="n">
+        <v>30.384640616919</v>
+      </c>
+      <c r="E40" t="n">
+        <v>-85.5565932283707</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>46</v>
+      </c>
+      <c r="B41" t="s">
+        <v>43</v>
+      </c>
+      <c r="C41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D41" t="n">
+        <v>29.8855555555556</v>
+      </c>
+      <c r="E41" t="n">
+        <v>-85.2436111111111</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42" t="s">
+        <v>44</v>
+      </c>
+      <c r="C42" t="s">
+        <v>7</v>
+      </c>
+      <c r="D42" t="n">
+        <v>29.8897222222222</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-85.2547222222222</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>45</v>
+      </c>
+      <c r="C43" t="s">
+        <v>7</v>
+      </c>
+      <c r="D43" t="n">
+        <v>30.1878333333333</v>
+      </c>
+      <c r="E43" t="n">
+        <v>-85.7416666666667</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -153,6 +153,57 @@
   </si>
   <si>
     <t xml:space="preserve">SA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SASal9</t>
   </si>
 </sst>
 </file>
@@ -1212,6 +1263,295 @@
         <v>-85.7416666666667</v>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>46</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="n">
+        <v>30.22818</v>
+      </c>
+      <c r="E44" t="n">
+        <v>-85.68972</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>48</v>
+      </c>
+      <c r="C45" t="s">
+        <v>11</v>
+      </c>
+      <c r="D45" t="n">
+        <v>30.13072</v>
+      </c>
+      <c r="E45" t="n">
+        <v>-85.60213</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>49</v>
+      </c>
+      <c r="C46" t="s">
+        <v>11</v>
+      </c>
+      <c r="D46" t="n">
+        <v>30.27551</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-85.73826</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>46</v>
+      </c>
+      <c r="B47" t="s">
+        <v>50</v>
+      </c>
+      <c r="C47" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" t="n">
+        <v>30.175</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-85.74167</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>46</v>
+      </c>
+      <c r="B48" t="s">
+        <v>51</v>
+      </c>
+      <c r="C48" t="s">
+        <v>11</v>
+      </c>
+      <c r="D48" t="n">
+        <v>30.0537</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-85.4027</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>46</v>
+      </c>
+      <c r="B49" t="s">
+        <v>52</v>
+      </c>
+      <c r="C49" t="s">
+        <v>11</v>
+      </c>
+      <c r="D49" t="n">
+        <v>30.06283</v>
+      </c>
+      <c r="E49" t="n">
+        <v>-85.43742</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>46</v>
+      </c>
+      <c r="B50" t="s">
+        <v>53</v>
+      </c>
+      <c r="C50" t="s">
+        <v>11</v>
+      </c>
+      <c r="D50" t="n">
+        <v>30.07733</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-85.50033</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>46</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
+        <v>11</v>
+      </c>
+      <c r="D51" t="n">
+        <v>30.036</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-85.44033</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>46</v>
+      </c>
+      <c r="B52" t="s">
+        <v>55</v>
+      </c>
+      <c r="C52" t="s">
+        <v>11</v>
+      </c>
+      <c r="D52" t="n">
+        <v>30.23473</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-85.59832</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>46</v>
+      </c>
+      <c r="B53" t="s">
+        <v>56</v>
+      </c>
+      <c r="C53" t="s">
+        <v>11</v>
+      </c>
+      <c r="D53" t="n">
+        <v>30.29567</v>
+      </c>
+      <c r="E53" t="n">
+        <v>-85.76333</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>46</v>
+      </c>
+      <c r="B54" t="s">
+        <v>57</v>
+      </c>
+      <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="n">
+        <v>30.1255</v>
+      </c>
+      <c r="E54" t="n">
+        <v>-85.56413</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>46</v>
+      </c>
+      <c r="B55" t="s">
+        <v>58</v>
+      </c>
+      <c r="C55" t="s">
+        <v>11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>30.27821</v>
+      </c>
+      <c r="E55" t="n">
+        <v>-85.80692</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>46</v>
+      </c>
+      <c r="B56" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" t="s">
+        <v>11</v>
+      </c>
+      <c r="D56" t="n">
+        <v>30.03833</v>
+      </c>
+      <c r="E56" t="n">
+        <v>-85.48667</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>46</v>
+      </c>
+      <c r="B57" t="s">
+        <v>60</v>
+      </c>
+      <c r="C57" t="s">
+        <v>11</v>
+      </c>
+      <c r="D57" t="n">
+        <v>30.14653</v>
+      </c>
+      <c r="E57" t="n">
+        <v>-85.65188</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>46</v>
+      </c>
+      <c r="B58" t="s">
+        <v>61</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58" t="n">
+        <v>30.16568</v>
+      </c>
+      <c r="E58" t="n">
+        <v>-85.77995</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>46</v>
+      </c>
+      <c r="B59" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" t="n">
+        <v>30.13129</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-85.73368</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>46</v>
+      </c>
+      <c r="B60" t="s">
+        <v>63</v>
+      </c>
+      <c r="C60" t="s">
+        <v>11</v>
+      </c>
+      <c r="D60" t="n">
+        <v>30.12638</v>
+      </c>
+      <c r="E60" t="n">
+        <v>-85.51812</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
+++ b/Water quality/Data/Raw-data/Flow_logger_locations.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="109">
   <si>
     <t xml:space="preserve">Site</t>
   </si>
@@ -204,6 +204,141 @@
   </si>
   <si>
     <t xml:space="preserve">SASal9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02300082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02300500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02300700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02301738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02301745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02306000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02306647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-023066535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02307000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02307498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02307674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02307780</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02308950</t>
+  </si>
+  <si>
+    <t xml:space="preserve">USGS-02309200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TBSal9</t>
   </si>
 </sst>
 </file>
@@ -1552,6 +1687,754 @@
         <v>-85.51812</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>64</v>
+      </c>
+      <c r="B61" t="s">
+        <v>65</v>
+      </c>
+      <c r="C61" t="s">
+        <v>7</v>
+      </c>
+      <c r="D61" t="n">
+        <v>27.5880555555556</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-82.5397222222222</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>64</v>
+      </c>
+      <c r="B62" t="s">
+        <v>66</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62" t="n">
+        <v>27.6711434369435</v>
+      </c>
+      <c r="E62" t="n">
+        <v>-82.3525924990226</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>64</v>
+      </c>
+      <c r="B63" t="s">
+        <v>67</v>
+      </c>
+      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="D63" t="n">
+        <v>27.7919756491865</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-82.3520866109009</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>64</v>
+      </c>
+      <c r="B64" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="D64" t="n">
+        <v>27.8800245705515</v>
+      </c>
+      <c r="E64" t="n">
+        <v>-82.3706484328483</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>64</v>
+      </c>
+      <c r="B65" t="s">
+        <v>69</v>
+      </c>
+      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="D65" t="n">
+        <v>27.9022459991089</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-82.3770374660052</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>70</v>
+      </c>
+      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="D66" t="n">
+        <v>28.0211348507913</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-82.4518113726457</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>64</v>
+      </c>
+      <c r="B67" t="s">
+        <v>71</v>
+      </c>
+      <c r="C67" t="s">
+        <v>7</v>
+      </c>
+      <c r="D67" t="n">
+        <v>28.013907747</v>
+      </c>
+      <c r="E67" t="n">
+        <v>-82.5450963479402</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>64</v>
+      </c>
+      <c r="B68" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" t="s">
+        <v>7</v>
+      </c>
+      <c r="D68" t="n">
+        <v>28.0000972222222</v>
+      </c>
+      <c r="E68" t="n">
+        <v>-82.5417666666667</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>64</v>
+      </c>
+      <c r="B69" t="s">
+        <v>73</v>
+      </c>
+      <c r="C69" t="s">
+        <v>7</v>
+      </c>
+      <c r="D69" t="n">
+        <v>28.036275</v>
+      </c>
+      <c r="E69" t="n">
+        <v>-82.5765722222222</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>64</v>
+      </c>
+      <c r="B70" t="s">
+        <v>74</v>
+      </c>
+      <c r="C70" t="s">
+        <v>7</v>
+      </c>
+      <c r="D70" t="n">
+        <v>28.0536283338892</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-82.7109335601835</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>64</v>
+      </c>
+      <c r="B71" t="s">
+        <v>75</v>
+      </c>
+      <c r="C71" t="s">
+        <v>7</v>
+      </c>
+      <c r="D71" t="n">
+        <v>27.9755061770307</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-82.713155811686</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>64</v>
+      </c>
+      <c r="B72" t="s">
+        <v>76</v>
+      </c>
+      <c r="C72" t="s">
+        <v>7</v>
+      </c>
+      <c r="D72" t="n">
+        <v>27.9158554470446</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-82.7248227513287</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>64</v>
+      </c>
+      <c r="B73" t="s">
+        <v>77</v>
+      </c>
+      <c r="C73" t="s">
+        <v>7</v>
+      </c>
+      <c r="D73" t="n">
+        <v>27.8102388888889</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-82.7203611111111</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" t="s">
+        <v>78</v>
+      </c>
+      <c r="C74" t="s">
+        <v>7</v>
+      </c>
+      <c r="D74" t="n">
+        <v>27.9424083333333</v>
+      </c>
+      <c r="E74" t="n">
+        <v>-82.804</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+      <c r="B75" t="s">
+        <v>79</v>
+      </c>
+      <c r="C75" t="s">
+        <v>11</v>
+      </c>
+      <c r="D75" t="n">
+        <v>27.77795</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-82.63042</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>64</v>
+      </c>
+      <c r="B76" t="s">
+        <v>80</v>
+      </c>
+      <c r="C76" t="s">
+        <v>11</v>
+      </c>
+      <c r="D76" t="n">
+        <v>27.7238</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-82.5338</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>64</v>
+      </c>
+      <c r="B77" t="s">
+        <v>81</v>
+      </c>
+      <c r="C77" t="s">
+        <v>11</v>
+      </c>
+      <c r="D77" t="n">
+        <v>27.79201</v>
+      </c>
+      <c r="E77" t="n">
+        <v>-82.35225</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+      <c r="B78" t="s">
+        <v>82</v>
+      </c>
+      <c r="C78" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" t="n">
+        <v>27.57205</v>
+      </c>
+      <c r="E78" t="n">
+        <v>-82.58834</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" t="s">
+        <v>83</v>
+      </c>
+      <c r="C79" t="s">
+        <v>11</v>
+      </c>
+      <c r="D79" t="n">
+        <v>27.6627</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-82.6679</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>64</v>
+      </c>
+      <c r="B80" t="s">
+        <v>84</v>
+      </c>
+      <c r="C80" t="s">
+        <v>11</v>
+      </c>
+      <c r="D80" t="n">
+        <v>27.67723</v>
+      </c>
+      <c r="E80" t="n">
+        <v>-82.496</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>64</v>
+      </c>
+      <c r="B81" t="s">
+        <v>85</v>
+      </c>
+      <c r="C81" t="s">
+        <v>11</v>
+      </c>
+      <c r="D81" t="n">
+        <v>27.7932</v>
+      </c>
+      <c r="E81" t="n">
+        <v>-82.5707</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>64</v>
+      </c>
+      <c r="B82" t="s">
+        <v>86</v>
+      </c>
+      <c r="C82" t="s">
+        <v>11</v>
+      </c>
+      <c r="D82" t="n">
+        <v>27.93205</v>
+      </c>
+      <c r="E82" t="n">
+        <v>-82.71472</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>64</v>
+      </c>
+      <c r="B83" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83" t="s">
+        <v>11</v>
+      </c>
+      <c r="D83" t="n">
+        <v>27.7813</v>
+      </c>
+      <c r="E83" t="n">
+        <v>-82.4741</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>64</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="n">
+        <v>27.7511</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-82.5718</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>64</v>
+      </c>
+      <c r="B85" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85" t="s">
+        <v>11</v>
+      </c>
+      <c r="D85" t="n">
+        <v>27.6279</v>
+      </c>
+      <c r="E85" t="n">
+        <v>-82.6415</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>64</v>
+      </c>
+      <c r="B86" t="s">
+        <v>90</v>
+      </c>
+      <c r="C86" t="s">
+        <v>11</v>
+      </c>
+      <c r="D86" t="n">
+        <v>27.81552</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-82.7405</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>64</v>
+      </c>
+      <c r="B87" t="s">
+        <v>91</v>
+      </c>
+      <c r="C87" t="s">
+        <v>11</v>
+      </c>
+      <c r="D87" t="n">
+        <v>27.5789</v>
+      </c>
+      <c r="E87" t="n">
+        <v>-82.7441</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>64</v>
+      </c>
+      <c r="B88" t="s">
+        <v>92</v>
+      </c>
+      <c r="C88" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" t="n">
+        <v>27.6245</v>
+      </c>
+      <c r="E88" t="n">
+        <v>-82.69285</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>64</v>
+      </c>
+      <c r="B89" t="s">
+        <v>93</v>
+      </c>
+      <c r="C89" t="s">
+        <v>11</v>
+      </c>
+      <c r="D89" t="n">
+        <v>27.51716</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-82.4231</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>64</v>
+      </c>
+      <c r="B90" t="s">
+        <v>94</v>
+      </c>
+      <c r="C90" t="s">
+        <v>11</v>
+      </c>
+      <c r="D90" t="n">
+        <v>27.55548</v>
+      </c>
+      <c r="E90" t="n">
+        <v>-82.38903</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>64</v>
+      </c>
+      <c r="B91" t="s">
+        <v>95</v>
+      </c>
+      <c r="C91" t="s">
+        <v>11</v>
+      </c>
+      <c r="D91" t="n">
+        <v>27.52881</v>
+      </c>
+      <c r="E91" t="n">
+        <v>-82.50519</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>64</v>
+      </c>
+      <c r="B92" t="s">
+        <v>96</v>
+      </c>
+      <c r="C92" t="s">
+        <v>11</v>
+      </c>
+      <c r="D92" t="n">
+        <v>27.9204</v>
+      </c>
+      <c r="E92" t="n">
+        <v>-82.81289</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>64</v>
+      </c>
+      <c r="B93" t="s">
+        <v>97</v>
+      </c>
+      <c r="C93" t="s">
+        <v>11</v>
+      </c>
+      <c r="D93" t="n">
+        <v>27.97376</v>
+      </c>
+      <c r="E93" t="n">
+        <v>-82.78193</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>64</v>
+      </c>
+      <c r="B94" t="s">
+        <v>98</v>
+      </c>
+      <c r="C94" t="s">
+        <v>11</v>
+      </c>
+      <c r="D94" t="n">
+        <v>27.89488</v>
+      </c>
+      <c r="E94" t="n">
+        <v>-82.77664</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>64</v>
+      </c>
+      <c r="B95" t="s">
+        <v>99</v>
+      </c>
+      <c r="C95" t="s">
+        <v>11</v>
+      </c>
+      <c r="D95" t="n">
+        <v>27.8162</v>
+      </c>
+      <c r="E95" t="n">
+        <v>-82.68339</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>64</v>
+      </c>
+      <c r="B96" t="s">
+        <v>100</v>
+      </c>
+      <c r="C96" t="s">
+        <v>11</v>
+      </c>
+      <c r="D96" t="n">
+        <v>27.86584</v>
+      </c>
+      <c r="E96" t="n">
+        <v>-82.61469</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>64</v>
+      </c>
+      <c r="B97" t="s">
+        <v>101</v>
+      </c>
+      <c r="C97" t="s">
+        <v>11</v>
+      </c>
+      <c r="D97" t="n">
+        <v>27.72839</v>
+      </c>
+      <c r="E97" t="n">
+        <v>-82.68608</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>64</v>
+      </c>
+      <c r="B98" t="s">
+        <v>102</v>
+      </c>
+      <c r="C98" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" t="n">
+        <v>27.58903</v>
+      </c>
+      <c r="E98" t="n">
+        <v>-82.49209</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>64</v>
+      </c>
+      <c r="B99" t="s">
+        <v>103</v>
+      </c>
+      <c r="C99" t="s">
+        <v>11</v>
+      </c>
+      <c r="D99" t="n">
+        <v>27.71155</v>
+      </c>
+      <c r="E99" t="n">
+        <v>-82.6203</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>64</v>
+      </c>
+      <c r="B100" t="s">
+        <v>104</v>
+      </c>
+      <c r="C100" t="s">
+        <v>11</v>
+      </c>
+      <c r="D100" t="n">
+        <v>27.88855</v>
+      </c>
+      <c r="E100" t="n">
+        <v>-82.40595</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>64</v>
+      </c>
+      <c r="B101" t="s">
+        <v>105</v>
+      </c>
+      <c r="C101" t="s">
+        <v>11</v>
+      </c>
+      <c r="D101" t="n">
+        <v>27.94689</v>
+      </c>
+      <c r="E101" t="n">
+        <v>-82.59995</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>64</v>
+      </c>
+      <c r="B102" t="s">
+        <v>106</v>
+      </c>
+      <c r="C102" t="s">
+        <v>11</v>
+      </c>
+      <c r="D102" t="n">
+        <v>27.68964</v>
+      </c>
+      <c r="E102" t="n">
+        <v>-82.45486</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>64</v>
+      </c>
+      <c r="B103" t="s">
+        <v>107</v>
+      </c>
+      <c r="C103" t="s">
+        <v>11</v>
+      </c>
+      <c r="D103" t="n">
+        <v>27.8118</v>
+      </c>
+      <c r="E103" t="n">
+        <v>-82.5232</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>64</v>
+      </c>
+      <c r="B104" t="s">
+        <v>108</v>
+      </c>
+      <c r="C104" t="s">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>27.778</v>
+      </c>
+      <c r="E104" t="n">
+        <v>-82.5203</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
